--- a/.schema/MHR_BUSHO.xlsx
+++ b/.schema/MHR_BUSHO.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KTC0966\git\sample\.schema\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t_fuk\git\sample\.schema\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2AB7272-B656-417A-A62D-DFD3BEE81E7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB7EBAA2-DE97-43FB-A885-51794F322CE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{16C90328-5CA8-4745-AEFC-BB3931E23911}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{16C90328-5CA8-4745-AEFC-BB3931E23911}"/>
   </bookViews>
   <sheets>
     <sheet name="EMARF.MHR_BUSHO" sheetId="2" r:id="rId1"/>
@@ -209,9 +209,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 テーマ">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -249,7 +249,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -355,7 +355,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -497,7 +497,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -563,14 +563,14 @@
       <c r="E3" s="3"/>
       <c r="F3" s="4" t="str">
         <f ca="1">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
-        <v>2026/07/22 14:55:43</v>
+        <v>2026/08/16 10:53:37</v>
       </c>
       <c r="G3" s="2">
         <v>0</v>
       </c>
       <c r="H3" s="4" t="str">
         <f t="shared" ref="H3:H8" ca="1" si="0">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
-        <v>2026/07/22 14:55:43</v>
+        <v>2026/08/16 10:53:37</v>
       </c>
       <c r="I3" s="2">
         <v>0</v>
@@ -590,14 +590,14 @@
       <c r="E4" s="3"/>
       <c r="F4" s="4" t="str">
         <f t="shared" ref="F4:F8" ca="1" si="1">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
-        <v>2026/07/22 14:55:43</v>
+        <v>2026/08/16 10:53:37</v>
       </c>
       <c r="G4" s="2">
         <v>0</v>
       </c>
       <c r="H4" s="4" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/07/22 14:55:43</v>
+        <v>2026/08/16 10:53:37</v>
       </c>
       <c r="I4" s="2">
         <v>0</v>
@@ -617,14 +617,14 @@
       <c r="E5" s="3"/>
       <c r="F5" s="4" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/07/22 14:55:43</v>
+        <v>2026/08/16 10:53:37</v>
       </c>
       <c r="G5" s="2">
         <v>0</v>
       </c>
       <c r="H5" s="4" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/07/22 14:55:43</v>
+        <v>2026/08/16 10:53:37</v>
       </c>
       <c r="I5" s="2">
         <v>0</v>
@@ -644,14 +644,14 @@
       <c r="E6" s="3"/>
       <c r="F6" s="4" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/07/22 14:55:43</v>
+        <v>2026/08/16 10:53:37</v>
       </c>
       <c r="G6" s="2">
         <v>0</v>
       </c>
       <c r="H6" s="4" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/07/22 14:55:43</v>
+        <v>2026/08/16 10:53:37</v>
       </c>
       <c r="I6" s="2">
         <v>0</v>
@@ -671,14 +671,14 @@
       <c r="E7" s="3"/>
       <c r="F7" s="4" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/07/22 14:55:43</v>
+        <v>2026/08/16 10:53:37</v>
       </c>
       <c r="G7" s="2">
         <v>0</v>
       </c>
       <c r="H7" s="4" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/07/22 14:55:43</v>
+        <v>2026/08/16 10:53:37</v>
       </c>
       <c r="I7" s="2">
         <v>0</v>
@@ -698,14 +698,14 @@
       <c r="E8" s="3"/>
       <c r="F8" s="4" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2026/07/22 14:55:43</v>
+        <v>2026/08/16 10:53:37</v>
       </c>
       <c r="G8" s="2">
         <v>0</v>
       </c>
       <c r="H8" s="4" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/07/22 14:55:43</v>
+        <v>2026/08/16 10:53:37</v>
       </c>
       <c r="I8" s="2">
         <v>0</v>
